--- a/appraiser_forms/018_property_appraisal_update_request_form--appraiser_forms.xlsx
+++ b/appraiser_forms/018_property_appraisal_update_request_form--appraiser_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bank_owned_reo</t>
+          <t>bank_owned_reo_with_lease</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bank Owned REO</t>
+          <t>Bank Owned REO with Lease</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>bank_owned_reo_with_lease</t>
+          <t>bank_owned_short_sale</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bank Owned REO with Lease</t>
+          <t>Bank Owned Short Sale</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>bank_owned_short_sale</t>
+          <t>bank_owned_with_rent</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bank Owned Short Sale</t>
+          <t>Bank Owned with Rent</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>bank_owned_with_rent</t>
+          <t>bank_owned_with_rent_&amp;_mortgage</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bank Owned with Rent</t>
+          <t>Bank Owned with Rent &amp; Mortgage</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bank_owned_with_rent_&amp;_mortgage</t>
+          <t>condo_sold</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bank Owned with Rent &amp; Mortgage</t>
+          <t>Condo Sold</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>condo_sold</t>
+          <t>foreclosure</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Condo Sold</t>
+          <t>Foreclosure</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>foreclosure</t>
+          <t>in_escrow</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Foreclosure</t>
+          <t>In Escrow</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>in_escrow</t>
+          <t>leased</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>In Escrow</t>
+          <t>Leased</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>leased</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Leased</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>pre-foreclosure</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Pre-foreclosure</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>pre-foreclosure</t>
+          <t>reo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pre-foreclosure</t>
+          <t>REO</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>reo</t>
+          <t>real_estate_owned</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>REO</t>
+          <t>Real Estate Owned</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>real_estate_owned</t>
+          <t>short_sale</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Real Estate Owned</t>
+          <t>Short Sale</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>short_sale</t>
+          <t>sold</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Short Sale</t>
+          <t>Sold</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sold</t>
+          <t>sold_to_another_lender</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sold</t>
+          <t>Sold to Another Lender</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sold_to_another_lender</t>
+          <t>sold_to_another_owner</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sold to Another Lender</t>
+          <t>Sold to Another Owner</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sold_to_another_owner</t>
+          <t>sold_to_lender</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sold to Another Owner</t>
+          <t>Sold to Lender</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>sold_to_lender</t>
+          <t>sold_to_owner</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sold to Lender</t>
+          <t>Sold to Owner</t>
         </is>
       </c>
     </row>
@@ -1607,27 +1607,10 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>sold_to_owner</t>
+          <t>vacant</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
-        <is>
-          <t>Sold to Owner</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>property_status_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>vacant</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
         <is>
           <t>Vacant</t>
         </is>
